--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supbrut_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supbrut_a_2020.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:07</t>
+    <t xml:space="preserve">2026-09-24 00:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -600,10 +600,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
         <v>-0.12</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11">
@@ -645,7 +645,7 @@
         <v>0.05</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12">
@@ -673,7 +673,7 @@
         <v>-0.2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14">
@@ -687,7 +687,7 @@
         <v>0.18</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         <v>-0.1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16">
